--- a/data/trans_bre/P57_AF_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 4,06</t>
+          <t>-3,46; 4,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 6,69</t>
+          <t>-0,83; 7,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 9,03</t>
+          <t>1,46; 9,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 8,09</t>
+          <t>-1,9; 8,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 6,23</t>
+          <t>-5,01; 6,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 10,45</t>
+          <t>-1,24; 11,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 12,24</t>
+          <t>1,85; 13,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 13,67</t>
+          <t>-2,89; 13,55</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,29</t>
+          <t>-2,4; 4,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 10,02</t>
+          <t>3,81; 10,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,25</t>
+          <t>-1,36; 4,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 28,39</t>
+          <t>-0,4; 28,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 7,6</t>
+          <t>-3,99; 7,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 16,92</t>
+          <t>6,14; 16,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,74</t>
+          <t>-1,8; 6,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 75,76</t>
+          <t>-0,96; 74,03</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 0,99</t>
+          <t>-11,39; 1,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 5,34</t>
+          <t>-8,44; 5,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 4,08</t>
+          <t>-7,31; 4,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 1,4</t>
+          <t>-9,57; 1,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 2,15</t>
+          <t>-18,96; 2,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 9,84</t>
+          <t>-13,43; 10,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 6,05</t>
+          <t>-10,59; 6,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 3,01</t>
+          <t>-17,36; 3,16</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,99</t>
+          <t>-1,92; 3,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,29</t>
+          <t>2,63; 7,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 4,35</t>
+          <t>-0,01; 4,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 21,61</t>
+          <t>0,32; 18,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,02</t>
+          <t>-3,07; 5,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 11,9</t>
+          <t>4,13; 12,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,92</t>
+          <t>0,01; 5,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 50,86</t>
+          <t>0,87; 42,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AF_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57_AF_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 4,16</t>
+          <t>-3,61; 3,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 7,47</t>
+          <t>-1,07; 6,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,46; 9,52</t>
+          <t>1,21; 8,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 8,12</t>
+          <t>-1,32; 8,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 6,45</t>
+          <t>-5,2; 6,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 11,67</t>
+          <t>-1,58; 10,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 13,01</t>
+          <t>1,5; 12,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 13,55</t>
+          <t>-1,99; 14,13</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 4,24</t>
+          <t>-2,25; 4,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,02</t>
+          <t>3,67; 10,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,48</t>
+          <t>-1,19; 4,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 28,18</t>
+          <t>-2,03; 4,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 7,51</t>
+          <t>-3,8; 7,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 16,97</t>
+          <t>6,01; 17,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,09</t>
+          <t>-1,53; 5,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 74,03</t>
+          <t>-3,38; 8,11</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,98</t>
+          <t>-3,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-7,76%</t>
+          <t>-6,24%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 1,16</t>
+          <t>-12,75; 1,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 5,62</t>
+          <t>-8,03; 5,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 4,27</t>
+          <t>-7,99; 3,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 1,52</t>
+          <t>-8,16; 2,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 2,02</t>
+          <t>-21,09; 2,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 10,23</t>
+          <t>-13,02; 10,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 6,79</t>
+          <t>-11,51; 5,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 3,16</t>
+          <t>-14,84; 4,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,05</t>
+          <t>-1,87; 3,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,35</t>
+          <t>2,43; 7,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,21</t>
+          <t>-0,07; 4,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 18,7</t>
+          <t>-1,26; 3,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,14</t>
+          <t>-3,0; 5,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 12,12</t>
+          <t>3,9; 11,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 5,79</t>
+          <t>-0,08; 5,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 42,94</t>
+          <t>-2,15; 6,39</t>
         </is>
       </c>
     </row>
